--- a/frozen_lair_monster_cards.xlsx
+++ b/frozen_lair_monster_cards.xlsx
@@ -33,7 +33,7 @@
     <t>Chill</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 2 Damage to each Adventurer.</t>
+    <t xml:space="preserve">Deal 4 Damage to each Adventurer.</t>
   </si>
   <si>
     <t>cardimages/flash_freeze.png</t>
@@ -60,7 +60,7 @@
     <t>Frostbite</t>
   </si>
   <si>
-    <t xml:space="preserve">Place below monster track. Each player takes 1 damage each turn. Remove when each player has taken unprevented damage.</t>
+    <t xml:space="preserve">Place below monster track. Each player takes 2 damage each turn. Remove when each player has taken unprevented damage.</t>
   </si>
   <si>
     <t>cardimages/time_seize.png</t>
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Time Seize</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 1 Damage to each Adventurer; monster goes first next round.</t>
+    <t xml:space="preserve">Deal 2 Damage to each Adventurer; monster goes first next round.</t>
   </si>
   <si>
     <t>cardimages/entomb.png</t>
@@ -78,7 +78,7 @@
     <t>Entomb</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 3 Damage to each Adventurer. If any wasn’t prevented, they still take 3 Damage.</t>
+    <t xml:space="preserve">Deal 6 Damage to each Adventurer. If any wasn’t prevented, they still take all 6 Damage.</t>
   </si>
   <si>
     <t>cardimages/wraith.png</t>
@@ -87,7 +87,7 @@
     <t>Wraith</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 1 Damage to each Adventurer; each must discard a card unless the Monster took 4+ Damage this turn.</t>
+    <t xml:space="preserve">Deal 2 Damage to each Adventurer; each must discard a card unless the Monster took 8+ Damage this turn.</t>
   </si>
   <si>
     <t>cardimages/blizzard.png</t>
